--- a/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
+++ b/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="246">
   <si>
     <t>MAP: TaxReturn</t>
   </si>
@@ -694,6 +694,9 @@
     <t>expected_nonresident_source_income</t>
   </si>
   <si>
+    <t>expense</t>
+  </si>
+  <si>
     <t>## CREATE ENTITIES (entity | tag | id | list)</t>
   </si>
   <si>
@@ -731,6 +734,9 @@
   </si>
   <si>
     <t>state_periods</t>
+  </si>
+  <si>
+    <t>expenses</t>
   </si>
   <si>
     <t>## ENTITIES (name | number: 1 or *)</t>
@@ -4213,159 +4219,159 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="6" t="s">
+      <c r="A234" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C234" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B234" s="6"/>
-      <c r="C234" s="6"/>
-      <c r="D234" s="6"/>
+      <c r="D234" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>6</v>
+        <v>226</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>227</v>
+        <v>8</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>6</v>
+        <v>226</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>228</v>
+        <v>11</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>6</v>
+        <v>226</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>229</v>
+        <v>11</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>6</v>
+        <v>226</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>230</v>
+        <v>15</v>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D239" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A239" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B239" s="6"/>
+      <c r="C239" s="6"/>
+      <c r="D239" s="6"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>6</v>
@@ -4376,311 +4382,337 @@
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D248" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D248" s="2" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
-        <v>235</v>
+        <v>166</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>235</v>
+        <v>166</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
-        <v>236</v>
+        <v>173</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>236</v>
+        <v>173</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>206</v>
+        <v>6</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="B253" s="6"/>
-      <c r="C253" s="6"/>
-      <c r="D253" s="6"/>
+      <c r="A253" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C254" s="2"/>
-      <c r="D254" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
-        <v>7</v>
+        <v>237</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C255" s="2"/>
-      <c r="D255" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C256" s="2"/>
-      <c r="D256" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
-        <v>32</v>
+        <v>219</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C257" s="2"/>
-      <c r="D257" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
-        <v>76</v>
+        <v>226</v>
       </c>
       <c r="B258" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="C258" s="2"/>
-      <c r="D258" s="2"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C259" s="2"/>
-      <c r="D259" s="2"/>
+      <c r="B259" s="6"/>
+      <c r="C259" s="6"/>
+      <c r="D259" s="6"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="s">
-        <v>122</v>
+        <v>7</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="s">
-        <v>130</v>
+        <v>237</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>134</v>
+        <v>32</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
-        <v>157</v>
+        <v>93</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" s="2"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="s">
-        <v>234</v>
+        <v>153</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" s="2"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="s">
-        <v>219</v>
+        <v>166</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
     </row>
     <row r="273">
-      <c r="A273" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="B273" s="6"/>
-      <c r="C273" s="6"/>
-      <c r="D273" s="6"/>
+      <c r="A273" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C273" s="2"/>
+      <c r="D273" s="2"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>243</v>
@@ -4690,7 +4722,7 @@
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>243</v>
@@ -4700,13 +4732,81 @@
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
-        <v>7</v>
+        <v>235</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>243</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C277" s="2"/>
+      <c r="D277" s="2"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C278" s="2"/>
+      <c r="D278" s="2"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C279" s="2"/>
+      <c r="D279" s="2"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B280" s="6"/>
+      <c r="C280" s="6"/>
+      <c r="D280" s="6"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C281" s="2"/>
+      <c r="D281" s="2"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C282" s="2"/>
+      <c r="D282" s="2"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C283" s="2"/>
+      <c r="D283" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
+++ b/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
   <si>
     <t>MAP: TaxReturn</t>
   </si>
@@ -695,6 +695,9 @@
   </si>
   <si>
     <t>expense</t>
+  </si>
+  <si>
+    <t>active_participation</t>
   </si>
   <si>
     <t>## CREATE ENTITIES (entity | tag | id | list)</t>
@@ -4289,33 +4292,33 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="6" t="s">
+      <c r="A239" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B239" s="6"/>
-      <c r="C239" s="6"/>
-      <c r="D239" s="6"/>
+      <c r="B239" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D240" s="2" t="s">
+      <c r="A240" s="6" t="s">
         <v>228</v>
       </c>
+      <c r="B240" s="6"/>
+      <c r="C240" s="6"/>
+      <c r="D240" s="6"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>6</v>
@@ -4326,10 +4329,10 @@
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -4340,10 +4343,10 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>6</v>
@@ -4354,10 +4357,10 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>6</v>
@@ -4368,10 +4371,10 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>6</v>
@@ -4382,10 +4385,10 @@
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>6</v>
@@ -4396,100 +4399,100 @@
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D253" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D253" s="2" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="254">
@@ -4503,7 +4506,7 @@
         <v>6</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="255">
@@ -4517,32 +4520,32 @@
         <v>6</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>206</v>
+        <v>6</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>6</v>
+        <v>206</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>239</v>
@@ -4550,10 +4553,10 @@
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>6</v>
@@ -4563,46 +4566,50 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="6" t="s">
+      <c r="A259" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D259" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B259" s="6"/>
-      <c r="C259" s="6"/>
-      <c r="D259" s="6"/>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B260" s="2" t="s">
+      <c r="A260" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="C260" s="2"/>
-      <c r="D260" s="2"/>
+      <c r="B260" s="6"/>
+      <c r="C260" s="6"/>
+      <c r="D260" s="6"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="s">
-        <v>7</v>
+        <v>237</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="s">
-        <v>237</v>
+        <v>7</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>32</v>
+        <v>238</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>243</v>
@@ -4612,201 +4619,211 @@
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" s="2"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" s="2"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" s="2"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" s="2"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" s="2"/>
     </row>
     <row r="280">
-      <c r="A280" s="6" t="s">
+      <c r="A280" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B280" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B280" s="6"/>
-      <c r="C280" s="6"/>
-      <c r="D280" s="6"/>
+      <c r="C280" s="2"/>
+      <c r="D280" s="2"/>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B281" s="2" t="s">
+      <c r="A281" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="C281" s="2"/>
-      <c r="D281" s="2"/>
+      <c r="B281" s="6"/>
+      <c r="C281" s="6"/>
+      <c r="D281" s="6"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" s="2"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="s">
-        <v>7</v>
+        <v>237</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C284" s="2"/>
+      <c r="D284" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
+++ b/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="248">
   <si>
     <t>MAP: TaxReturn</t>
   </si>
@@ -698,6 +698,9 @@
   </si>
   <si>
     <t>active_participation</t>
+  </si>
+  <si>
+    <t>expected_state_tax</t>
   </si>
   <si>
     <t>## CREATE ENTITIES (entity | tag | id | list)</t>
@@ -4306,33 +4309,33 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="6" t="s">
+      <c r="A240" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B240" s="6"/>
-      <c r="C240" s="6"/>
-      <c r="D240" s="6"/>
+      <c r="B240" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D241" s="2" t="s">
+      <c r="A241" s="6" t="s">
         <v>229</v>
       </c>
+      <c r="B241" s="6"/>
+      <c r="C241" s="6"/>
+      <c r="D241" s="6"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -4343,10 +4346,10 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>6</v>
@@ -4357,10 +4360,10 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>6</v>
@@ -4371,10 +4374,10 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>6</v>
@@ -4385,10 +4388,10 @@
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>6</v>
@@ -4399,10 +4402,10 @@
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>6</v>
@@ -4413,100 +4416,100 @@
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D254" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="255">
@@ -4520,7 +4523,7 @@
         <v>6</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="256">
@@ -4534,32 +4537,32 @@
         <v>6</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>206</v>
+        <v>6</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>6</v>
+        <v>206</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>240</v>
@@ -4567,10 +4570,10 @@
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>6</v>
@@ -4580,46 +4583,50 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="6" t="s">
+      <c r="A260" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D260" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B260" s="6"/>
-      <c r="C260" s="6"/>
-      <c r="D260" s="6"/>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B261" s="2" t="s">
+      <c r="A261" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="C261" s="2"/>
-      <c r="D261" s="2"/>
+      <c r="B261" s="6"/>
+      <c r="C261" s="6"/>
+      <c r="D261" s="6"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="s">
-        <v>7</v>
+        <v>238</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>238</v>
+        <v>7</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>32</v>
+        <v>239</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>244</v>
@@ -4629,201 +4636,211 @@
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" s="2"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" s="2"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" s="2"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" s="2"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" s="2"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" s="2"/>
     </row>
     <row r="281">
-      <c r="A281" s="6" t="s">
+      <c r="A281" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B281" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B281" s="6"/>
-      <c r="C281" s="6"/>
-      <c r="D281" s="6"/>
+      <c r="C281" s="2"/>
+      <c r="D281" s="2"/>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B282" s="2" t="s">
+      <c r="A282" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="C282" s="2"/>
-      <c r="D282" s="2"/>
+      <c r="B282" s="6"/>
+      <c r="C282" s="6"/>
+      <c r="D282" s="6"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="s">
-        <v>7</v>
+        <v>238</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" s="2"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C285" s="2"/>
+      <c r="D285" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
+++ b/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
   <si>
     <t>MAP: TaxReturn</t>
   </si>
@@ -701,6 +701,9 @@
   </si>
   <si>
     <t>expected_state_tax</t>
+  </si>
+  <si>
+    <t>military_retirement_pay</t>
   </si>
   <si>
     <t>## CREATE ENTITIES (entity | tag | id | list)</t>
@@ -4323,33 +4326,33 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="6" t="s">
+      <c r="A241" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B241" s="6"/>
-      <c r="C241" s="6"/>
-      <c r="D241" s="6"/>
+      <c r="B241" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D242" s="2" t="s">
+      <c r="A242" s="6" t="s">
         <v>230</v>
       </c>
+      <c r="B242" s="6"/>
+      <c r="C242" s="6"/>
+      <c r="D242" s="6"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>6</v>
@@ -4360,10 +4363,10 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>6</v>
@@ -4374,10 +4377,10 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>6</v>
@@ -4388,10 +4391,10 @@
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>6</v>
@@ -4402,10 +4405,10 @@
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>6</v>
@@ -4416,10 +4419,10 @@
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>6</v>
@@ -4430,100 +4433,100 @@
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D255" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D255" s="2" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="256">
@@ -4537,7 +4540,7 @@
         <v>6</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="257">
@@ -4551,32 +4554,32 @@
         <v>6</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>206</v>
+        <v>6</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>6</v>
+        <v>206</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>241</v>
@@ -4584,10 +4587,10 @@
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>6</v>
@@ -4597,46 +4600,50 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="6" t="s">
+      <c r="A261" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D261" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B261" s="6"/>
-      <c r="C261" s="6"/>
-      <c r="D261" s="6"/>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B262" s="2" t="s">
+      <c r="A262" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="C262" s="2"/>
-      <c r="D262" s="2"/>
+      <c r="B262" s="6"/>
+      <c r="C262" s="6"/>
+      <c r="D262" s="6"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>7</v>
+        <v>239</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>239</v>
+        <v>7</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
-        <v>32</v>
+        <v>240</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>245</v>
@@ -4646,201 +4653,211 @@
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" s="2"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" s="2"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" s="2"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" s="2"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>237</v>
+        <v>196</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" s="2"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" s="2"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" s="2"/>
     </row>
     <row r="282">
-      <c r="A282" s="6" t="s">
+      <c r="A282" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B282" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B282" s="6"/>
-      <c r="C282" s="6"/>
-      <c r="D282" s="6"/>
+      <c r="C282" s="2"/>
+      <c r="D282" s="2"/>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B283" s="2" t="s">
+      <c r="A283" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="C283" s="2"/>
-      <c r="D283" s="2"/>
+      <c r="B283" s="6"/>
+      <c r="C283" s="6"/>
+      <c r="D283" s="6"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" s="2"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="s">
-        <v>7</v>
+        <v>239</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" s="2"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C286" s="2"/>
+      <c r="D286" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
